--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.110.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.110.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.110.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.110.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="49" customWidth="1" min="14" max="14"/>
-    <col width="49" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.110.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.110.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0110.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0110.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -601,16 +601,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ed all matters of accountâ€”questions as to priority of en-</t>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: brought in by the time appointed for that purpose ； and a</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: THE MASTERâ€™S OFFICE.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]103</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]103</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L21: isolated marker/symbol line :: 103</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L47: isolated marker/symbol line :: :</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]103</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -649,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -658,16 +662,8 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L52: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: administration suits â€” the appointment of Receivers and</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L12: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: reader is referred to that very useful work, " Bennettâ€™s</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -677,7 +673,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: %</t>
+          <t>L47: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -718,11 +714,7 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN, U+FFFD REPLACEMENT CHARACTER :: Chancery Practice in the Masterâ€™s Office,â€� which is re-</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -732,7 +724,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L90: symbol-only separator/garbage line :: 847,</t>
+          <t>L70: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -754,12 +746,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -769,17 +761,13 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ed all matters of accountâ€”questions as to priority of en-</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr"/>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line :: %</t>
+          <t>L90: symbol-only separator/garbage line :: 847,</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -816,17 +804,13 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L25: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: cumbrancesâ€”of the validity of titles in specific perform-</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr"/>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L102: isolated marker/symbol line :: /</t>
+          <t>L100: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -863,17 +847,13 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ance and other casesâ€”of legacies, and their payment in</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr"/>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L104: isolated marker/symbol line :: -</t>
+          <t>L102: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -910,17 +890,13 @@
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: administration suitsâ€”the appointment of Receivers and</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr"/>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L106: isolated marker/symbol line :: *</t>
+          <t>L104: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -957,15 +933,15 @@
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Guardians,â€”enquiries as to the estates and the mainten-</t>
-        </is>
-      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr"/>
-      <c r="O9" s="1" t="inlineStr"/>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>L106: isolated marker/symbol line :: *</t>
+        </is>
+      </c>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
       <c r="R9" s="1" t="inlineStr"/>
@@ -985,12 +961,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1000,11 +976,7 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: terâ€™s) Enter-</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr"/>
@@ -1033,7 +1005,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1072,7 +1044,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
